--- a/public/math-game/authoring/khshab-G2-MATH_v0.2.xlsx
+++ b/public/math-game/authoring/khshab-G2-MATH_v0.2.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="شناسنامهٔ خشاب" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="نقشهٔ کتاب (S1)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="اطلس خطا" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="بانک سؤال" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="واژه‌نامهٔ ستون‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="پروتکل ممیزی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="شناسنامهٔ خشاب" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نقشهٔ کتاب (S1)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اطلس خطا" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بانک سؤال" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="واژه‌نامهٔ ستون‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="پروتکل ممیزی" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'نقشهٔ کتاب (S1)'!$A$2:$N$4</definedName>
@@ -947,12 +947,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰؛ شاهد: صفحهٔ شناسنامهٔ فایل C205.pdf — هنوز «نیاز به تأیید» است تا تأیید معلّم با کتاب فیزیکی</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰؛ شاهد: صفحهٔ شناسنامهٔ فایل C205.pdf — هنوز «نیاز به تأیید» است تا تأیید معلّم با کتاب فیزیکی</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>در تألیف — v0.2 (موج ۱، اسکلت: شناسنامهٔ تکمیل‌شده از PDF کتاب + ۸ ردیف گسترهٔ فصل در S1؛ بدون سؤال و بدون اطلس)</t>
+          <t>در تألیف — v0.2 (موج ۱، اسکلت: شناسنامهٔ تکمیل‌شده از PDF کتاب + ۸ ردیف گسترهٔ فصل در S1؛ بدون سؤال و بدون اطلس) — اسکلت موج ۱ سبز شد</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>باز — منتظر معلمِ در دسترس کتاب فیزیکی</t>
+          <t>معلم پروژه — تأیید شفاهی با کتاب فیزیکی (موج ۱)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>۲۰۲۶-۱۰-۲۱ — موج ۱ (اسکلت ۸ فصلی)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>پیش‌پُر موتور تألیف v۱.۰</t>
+          <t>کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>پیشنهاد AI — موتور تألیف v۱.۰</t>
+          <t>پیشنهاد AI — موتور تألیف v۱.۰؛ تأیید: کتاب فیزیکی معلم — چاپ چهاردهم ۱۴۰۴ + راستی‌آزمایی عکس (شناسنامه/فهرست/پایان C205) + تأیید شفاهی معلم</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>نیاز به تأیید</t>
+          <t>تأییدشده</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
